--- a/Backtest/11-09-20/S&P500stock_11-09-20period252RS90.xlsx
+++ b/Backtest/11-09-20/S&P500stock_11-09-20period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>Stock</t>
   </si>
@@ -127,79 +127,118 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>CHTR</t>
+    <t>HOLX</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>POOL</t>
+  </si>
+  <si>
+    <t>RVTY</t>
+  </si>
+  <si>
+    <t>ALGN</t>
   </si>
   <si>
     <t>CRWD</t>
   </si>
   <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>DHR</t>
-  </si>
-  <si>
-    <t>ADBE</t>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t>MKTX</t>
   </si>
   <si>
     <t>WST</t>
   </si>
   <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
-    <t>2020-10-30</t>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-11-24</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
   </si>
   <si>
     <t>2020-12-02</t>
   </si>
   <si>
-    <t>2020-10-27</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>2020-09-15</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Integrated Freight &amp; Logistics</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Telecom Services</t>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
   </si>
   <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Medical Care Facilities</t>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Solar</t>
   </si>
 </sst>
 </file>
@@ -557,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -678,43 +717,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>94.93927125506073</v>
+        <v>90.30303030303031</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="D2">
-        <v>247.8</v>
+        <v>75.05</v>
       </c>
       <c r="E2">
-        <v>6.37</v>
+        <v>2.01</v>
       </c>
       <c r="F2">
-        <v>1.936874497502236</v>
+        <v>-0.4784050858116398</v>
       </c>
       <c r="G2">
-        <v>4.03</v>
+        <v>2.11</v>
       </c>
       <c r="H2">
-        <v>1.144691215298686</v>
+        <v>-0.4813297436647671</v>
       </c>
       <c r="I2">
-        <v>251.8420013427734</v>
+        <v>73.58999938964844</v>
       </c>
       <c r="J2">
-        <v>237.2775016784668</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="K2">
-        <v>211.5190008544922</v>
+        <v>65.76799995422363</v>
       </c>
       <c r="L2">
-        <v>179.2483501434326</v>
+        <v>55.51869997024536</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -726,61 +765,61 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>115.29</v>
+        <v>26.49</v>
       </c>
       <c r="Y2">
-        <v>284.5</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="Z2">
-        <v>179.65</v>
+        <v>17.59</v>
       </c>
       <c r="AA2">
-        <v>-1401.66</v>
+        <v>143.03</v>
       </c>
       <c r="AB2">
-        <v>125.89</v>
+        <v>523.53</v>
       </c>
       <c r="AC2">
-        <v>2516.67</v>
+        <v>31.94</v>
       </c>
       <c r="AD2">
-        <v>6.83</v>
+        <v>18.23</v>
       </c>
       <c r="AE2">
-        <v>2536.36</v>
+        <v>258.49</v>
       </c>
       <c r="AF2">
-        <v>130.56</v>
+        <v>43.24</v>
       </c>
       <c r="AG2">
-        <v>-200</v>
+        <v>-74.31</v>
       </c>
       <c r="AH2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AJ2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="AK2">
-        <v>85.43573753480412</v>
+        <v>62.13444315232041</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -788,109 +827,109 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>90.08097165991903</v>
+        <v>92.92929292929293</v>
       </c>
       <c r="C3">
-        <v>366</v>
+        <v>244</v>
       </c>
       <c r="D3">
-        <v>604.0599999999999</v>
+        <v>279.77</v>
       </c>
       <c r="E3">
-        <v>1.05</v>
+        <v>2.4</v>
       </c>
       <c r="F3">
-        <v>-1.110570183225866</v>
+        <v>-0.2618413550022634</v>
       </c>
       <c r="G3">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="H3">
-        <v>-1.146673364589247</v>
+        <v>-0.5723080635497066</v>
       </c>
       <c r="I3">
-        <v>605.1920043945313</v>
+        <v>273.8800048828125</v>
       </c>
       <c r="J3">
-        <v>610.5529968261719</v>
+        <v>275.3764984130859</v>
       </c>
       <c r="K3">
-        <v>581.6997973632813</v>
+        <v>255.5997988891602</v>
       </c>
       <c r="L3">
-        <v>515.8921990966796</v>
+        <v>171.4473996734619</v>
       </c>
       <c r="M3">
         <v>0.99</v>
       </c>
       <c r="N3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P3">
+        <v>6</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
         <v>5</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>3.888888888888888</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>345.67</v>
+        <v>88.69</v>
       </c>
       <c r="Y3">
-        <v>629.52</v>
+        <v>293.3</v>
       </c>
       <c r="Z3">
-        <v>107.57</v>
+        <v>57.82</v>
       </c>
       <c r="AA3">
-        <v>-34.05</v>
+        <v>3.4</v>
       </c>
       <c r="AB3">
-        <v>38.47</v>
+        <v>73.72</v>
       </c>
       <c r="AC3">
-        <v>110.17</v>
+        <v>120.93</v>
       </c>
       <c r="AD3">
-        <v>2.41</v>
+        <v>6.4</v>
       </c>
       <c r="AE3">
-        <v>94.76000000000001</v>
+        <v>465.38</v>
       </c>
       <c r="AF3">
-        <v>-41.95</v>
+        <v>-207.44</v>
       </c>
       <c r="AG3">
-        <v>85.88</v>
+        <v>-43.72</v>
       </c>
       <c r="AH3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AI3" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="AJ3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="AK3">
-        <v>53.80335592941188</v>
+        <v>59.92436658532922</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -898,58 +937,58 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.77327935222672</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C4">
-        <v>58</v>
+        <v>326</v>
       </c>
       <c r="D4">
-        <v>129.35</v>
+        <v>259.41</v>
       </c>
       <c r="E4">
-        <v>4.31</v>
+        <v>2.28</v>
       </c>
       <c r="F4">
-        <v>0.7568489256413541</v>
+        <v>-0.3284763490974562</v>
       </c>
       <c r="G4">
-        <v>3.81</v>
+        <v>2.33</v>
       </c>
       <c r="H4">
-        <v>0.9702620777293622</v>
+        <v>-0.2589382950571364</v>
       </c>
       <c r="I4">
-        <v>127.5199996948242</v>
+        <v>250.0540008544922</v>
       </c>
       <c r="J4">
-        <v>118.7012500762939</v>
+        <v>249.4689987182617</v>
       </c>
       <c r="K4">
-        <v>111.5980999755859</v>
+        <v>239.5973986816406</v>
       </c>
       <c r="L4">
-        <v>77.06352493286133</v>
+        <v>212.5621999359131</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -961,46 +1000,46 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>31.95</v>
+        <v>125.38</v>
       </c>
       <c r="Y4">
-        <v>153.1</v>
+        <v>268.44</v>
       </c>
       <c r="Z4">
-        <v>24.53</v>
+        <v>52.53</v>
       </c>
       <c r="AA4">
-        <v>0.15</v>
+        <v>-23.44</v>
       </c>
       <c r="AB4">
-        <v>91.18000000000001</v>
+        <v>196.43</v>
       </c>
       <c r="AC4">
-        <v>17.65</v>
+        <v>50</v>
       </c>
       <c r="AD4">
-        <v>-3.77</v>
+        <v>145.91</v>
       </c>
       <c r="AE4">
-        <v>-55.56</v>
+        <v>50</v>
       </c>
       <c r="AF4">
-        <v>-156.25</v>
+        <v>-50.82</v>
       </c>
       <c r="AG4">
-        <v>194.12</v>
+        <v>103.33</v>
       </c>
       <c r="AH4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AI4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AJ4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AK4">
-        <v>51.37526503721096</v>
+        <v>55.00172240126079</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1008,43 +1047,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>98.98785425101214</v>
+        <v>98.58585858585859</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>78.98</v>
+        <v>85.88</v>
       </c>
       <c r="E5">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="F5">
-        <v>0.149651301285755</v>
+        <v>-0.1285713668118778</v>
       </c>
       <c r="G5">
-        <v>4.23</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
-        <v>1.303263158543526</v>
+        <v>0.317257730880815</v>
       </c>
       <c r="I5">
-        <v>80.82600250244141</v>
+        <v>80.30199890136718</v>
       </c>
       <c r="J5">
-        <v>83.8520004272461</v>
+        <v>80.82749900817871</v>
       </c>
       <c r="K5">
-        <v>73.26599998474121</v>
+        <v>81.2368002319336</v>
       </c>
       <c r="L5">
-        <v>55.18095001220703</v>
+        <v>62.49494997024536</v>
       </c>
       <c r="M5">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1065,52 +1104,52 @@
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>27.43</v>
+        <v>35.58</v>
       </c>
       <c r="Y5">
         <v>94.28</v>
       </c>
       <c r="Z5">
-        <v>64.55</v>
+        <v>99.62</v>
       </c>
       <c r="AA5">
-        <v>-8.029999999999999</v>
+        <v>-8.85</v>
       </c>
       <c r="AB5">
-        <v>86.20999999999999</v>
+        <v>116.97</v>
       </c>
       <c r="AC5">
-        <v>18.18</v>
+        <v>105.88</v>
       </c>
       <c r="AD5">
-        <v>4.75</v>
+        <v>10.09</v>
       </c>
       <c r="AE5">
+        <v>153.38</v>
+      </c>
+      <c r="AF5">
         <v>-7.14</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>-12.5</v>
       </c>
-      <c r="AG5">
-        <v>45.45</v>
-      </c>
       <c r="AH5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AI5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AJ5" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="AK5">
-        <v>44.56630836186529</v>
+        <v>54.50544855103065</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1118,46 +1157,46 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>91.09311740890689</v>
+        <v>97.17171717171718</v>
       </c>
       <c r="C6">
-        <v>201</v>
+        <v>476</v>
       </c>
       <c r="D6">
-        <v>180.04</v>
+        <v>382.89</v>
       </c>
       <c r="E6">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="F6">
-        <v>-0.8356127684233307</v>
+        <v>-0.639439654875022</v>
       </c>
       <c r="G6">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="H6">
-        <v>-0.9881014213444068</v>
+        <v>-0.7340472989007105</v>
       </c>
       <c r="I6">
-        <v>177.0691528320312</v>
+        <v>373.0900085449219</v>
       </c>
       <c r="J6">
-        <v>181.716756439209</v>
+        <v>361.5120010375977</v>
       </c>
       <c r="K6">
-        <v>176.1164898681641</v>
+        <v>334.5430023193359</v>
       </c>
       <c r="L6">
-        <v>147.587322883606</v>
+        <v>268.3046504974365</v>
       </c>
       <c r="M6">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <v>2</v>
@@ -1169,58 +1208,58 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>7.777777777777777</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>106.03</v>
+        <v>160.35</v>
       </c>
       <c r="Y6">
-        <v>186.68</v>
+        <v>391.5</v>
       </c>
       <c r="Z6">
-        <v>112.59</v>
+        <v>13.66</v>
       </c>
       <c r="AA6">
-        <v>2.89</v>
+        <v>18.81</v>
       </c>
       <c r="AB6">
-        <v>9.17</v>
+        <v>15.98</v>
       </c>
       <c r="AC6">
-        <v>41.11</v>
+        <v>560</v>
       </c>
       <c r="AD6">
-        <v>2.81</v>
+        <v>20.2</v>
       </c>
       <c r="AE6">
-        <v>53.01</v>
+        <v>-24.62</v>
       </c>
       <c r="AF6">
-        <v>-52.84</v>
+        <v>411.69</v>
       </c>
       <c r="AG6">
-        <v>95.56</v>
+        <v>71.11</v>
       </c>
       <c r="AH6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AI6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AJ6" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="AK6">
-        <v>37.6774070291243</v>
+        <v>47.29007746116118</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1228,43 +1267,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>96.35627530364373</v>
+        <v>90.1010101010101</v>
       </c>
       <c r="C7">
-        <v>153</v>
+        <v>383</v>
       </c>
       <c r="D7">
-        <v>476.26</v>
+        <v>141.3</v>
       </c>
       <c r="E7">
-        <v>3.35</v>
+        <v>1.75</v>
       </c>
       <c r="F7">
-        <v>0.2069340960362833</v>
+        <v>-0.6227809063512239</v>
       </c>
       <c r="G7">
-        <v>2.51</v>
+        <v>1.84</v>
       </c>
       <c r="H7">
-        <v>-0.06045555336209539</v>
+        <v>-0.7542647033195859</v>
       </c>
       <c r="I7">
-        <v>483.5179992675781</v>
+        <v>136.1079986572266</v>
       </c>
       <c r="J7">
-        <v>486.7565002441406</v>
+        <v>127.7754993438721</v>
       </c>
       <c r="K7">
-        <v>461.0000006103515</v>
+        <v>123.3798001098633</v>
       </c>
       <c r="L7">
-        <v>377.472300567627</v>
+        <v>102.3270000457764</v>
       </c>
       <c r="M7">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1285,52 +1324,52 @@
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>255.13</v>
+        <v>62.91</v>
       </c>
       <c r="Y7">
-        <v>536.88</v>
+        <v>142.65</v>
       </c>
       <c r="Z7">
-        <v>187.5</v>
+        <v>14.09</v>
       </c>
       <c r="AA7">
-        <v>128.78</v>
+        <v>15.86</v>
       </c>
       <c r="AB7">
-        <v>8.359999999999999</v>
+        <v>37.04</v>
       </c>
       <c r="AC7">
-        <v>39.88</v>
+        <v>167.8</v>
       </c>
       <c r="AD7">
-        <v>10.11</v>
+        <v>5.47</v>
       </c>
       <c r="AE7">
-        <v>15.15</v>
+        <v>28.46</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>310</v>
       </c>
       <c r="AG7">
-        <v>7.98</v>
+        <v>-49.15</v>
       </c>
       <c r="AH7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AJ7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AK7">
-        <v>26.59685568055053</v>
+        <v>44.43504704693497</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1338,43 +1377,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>97.97570850202429</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="C8">
-        <v>463</v>
+        <v>404</v>
       </c>
       <c r="D8">
-        <v>275.38</v>
+        <v>477.85</v>
       </c>
       <c r="E8">
-        <v>2.35</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F8">
-        <v>-0.3658938514689991</v>
+        <v>2.964402942439984</v>
       </c>
       <c r="G8">
-        <v>1.89</v>
+        <v>5.08</v>
       </c>
       <c r="H8">
-        <v>-0.552028577421098</v>
+        <v>2.520954812538244</v>
       </c>
       <c r="I8">
-        <v>268.3059997558594</v>
+        <v>475.3340026855469</v>
       </c>
       <c r="J8">
-        <v>273.9475006103515</v>
+        <v>409.0665023803711</v>
       </c>
       <c r="K8">
-        <v>261.8409994506836</v>
+        <v>354.9978002929687</v>
       </c>
       <c r="L8">
-        <v>193.6186494445801</v>
+        <v>272.3649496459961</v>
       </c>
       <c r="M8">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="N8">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1398,49 +1437,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>124.53</v>
+        <v>127.88</v>
       </c>
       <c r="Y8">
-        <v>288.65</v>
+        <v>498.67</v>
       </c>
       <c r="Z8">
-        <v>17.15</v>
+        <v>25.91</v>
       </c>
       <c r="AA8">
-        <v>25.27</v>
+        <v>83.59</v>
       </c>
       <c r="AB8">
-        <v>0.26</v>
+        <v>225.63</v>
       </c>
       <c r="AC8">
-        <v>63.16</v>
+        <v>14.94</v>
       </c>
       <c r="AD8">
-        <v>5.68</v>
+        <v>4.59</v>
       </c>
       <c r="AE8">
-        <v>22.77</v>
+        <v>440.38</v>
       </c>
       <c r="AF8">
-        <v>17.44</v>
+        <v>-102.69</v>
       </c>
       <c r="AG8">
-        <v>13.16</v>
+        <v>1154.55</v>
       </c>
       <c r="AH8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AJ8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AK8">
-        <v>8.815808631755646</v>
+        <v>44.20254322089296</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1448,109 +1487,659 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>91.49797570850203</v>
+        <v>99.19191919191918</v>
       </c>
       <c r="C9">
-        <v>329</v>
+        <v>224</v>
       </c>
       <c r="D9">
-        <v>87.59</v>
+        <v>141.79</v>
       </c>
       <c r="E9">
-        <v>1.7</v>
+        <v>2.89</v>
       </c>
       <c r="F9">
-        <v>-0.7382320173474327</v>
+        <v>0.01025153755310698</v>
       </c>
       <c r="G9">
-        <v>1.74</v>
+        <v>3.31</v>
       </c>
       <c r="H9">
-        <v>-0.6709575348547276</v>
+        <v>0.7317145214677628</v>
       </c>
       <c r="I9">
-        <v>87.02199859619141</v>
+        <v>133.6720001220703</v>
       </c>
       <c r="J9">
-        <v>86.5854995727539</v>
+        <v>137.3669998168945</v>
       </c>
       <c r="K9">
-        <v>85.21020004272461</v>
+        <v>135.9424002075195</v>
       </c>
       <c r="L9">
-        <v>79.40799983978272</v>
+        <v>94.17097494125366</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="N9">
+        <v>0.98</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>5</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>31.95</v>
+      </c>
+      <c r="Y9">
+        <v>153.9</v>
+      </c>
+      <c r="Z9">
+        <v>24.53</v>
+      </c>
+      <c r="AA9">
+        <v>0.15</v>
+      </c>
+      <c r="AB9">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>17.65</v>
+      </c>
+      <c r="AD9">
+        <v>-3.77</v>
+      </c>
+      <c r="AE9">
+        <v>-55.56</v>
+      </c>
+      <c r="AF9">
+        <v>-156.25</v>
+      </c>
+      <c r="AG9">
+        <v>194.12</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK9">
+        <v>36.74277494030434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>97.97979797979798</v>
+      </c>
+      <c r="C10">
+        <v>463</v>
+      </c>
+      <c r="D10">
+        <v>357.18</v>
+      </c>
+      <c r="E10">
+        <v>2.79</v>
+      </c>
+      <c r="F10">
+        <v>-0.04527762419288699</v>
+      </c>
+      <c r="G10">
+        <v>2.71</v>
+      </c>
+      <c r="H10">
+        <v>0.1251923889014979</v>
+      </c>
+      <c r="I10">
+        <v>335.8580017089844</v>
+      </c>
+      <c r="J10">
+        <v>320.8055038452148</v>
+      </c>
+      <c r="K10">
+        <v>288.4184014892578</v>
+      </c>
+      <c r="L10">
+        <v>228.076350479126</v>
+      </c>
+      <c r="M10">
+        <v>1.05</v>
+      </c>
+      <c r="N10">
+        <v>1.16</v>
+      </c>
+      <c r="P10">
+        <v>4</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>130.12</v>
+      </c>
+      <c r="Y10">
+        <v>358.69</v>
+      </c>
+      <c r="Z10">
+        <v>13.13</v>
+      </c>
+      <c r="AA10">
+        <v>55.17</v>
+      </c>
+      <c r="AB10">
+        <v>9.15</v>
+      </c>
+      <c r="AC10">
+        <v>65.33</v>
+      </c>
+      <c r="AD10">
+        <v>6.08</v>
+      </c>
+      <c r="AE10">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="AF10">
+        <v>-16.25</v>
+      </c>
+      <c r="AG10">
+        <v>6.67</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK10">
+        <v>23.68370014020816</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>94.34343434343434</v>
+      </c>
+      <c r="C11">
+        <v>304</v>
+      </c>
+      <c r="D11">
+        <v>527.66</v>
+      </c>
+      <c r="E11">
+        <v>1.54</v>
+      </c>
+      <c r="F11">
+        <v>-0.739392146017811</v>
+      </c>
+      <c r="G11">
+        <v>1.58</v>
+      </c>
+      <c r="H11">
+        <v>-1.017090960764967</v>
+      </c>
+      <c r="I11">
+        <v>505.0879943847656</v>
+      </c>
+      <c r="J11">
+        <v>480.5379989624024</v>
+      </c>
+      <c r="K11">
+        <v>451.3954022216797</v>
+      </c>
+      <c r="L11">
+        <v>372.7496506500244</v>
+      </c>
+      <c r="M11">
+        <v>1.05</v>
+      </c>
+      <c r="N11">
+        <v>1.12</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>250.21</v>
+      </c>
+      <c r="Y11">
+        <v>532.5700000000001</v>
+      </c>
+      <c r="Z11">
+        <v>176.17</v>
+      </c>
+      <c r="AA11">
+        <v>5.89</v>
+      </c>
+      <c r="AB11">
+        <v>7.14</v>
+      </c>
+      <c r="AC11">
+        <v>94.42</v>
+      </c>
+      <c r="AD11">
+        <v>6.07</v>
+      </c>
+      <c r="AE11">
+        <v>67.12</v>
+      </c>
+      <c r="AF11">
+        <v>46.73</v>
+      </c>
+      <c r="AG11">
+        <v>-20.72</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK11">
+        <v>19.56138486165915</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>91.51515151515152</v>
+      </c>
+      <c r="C12">
+        <v>487</v>
+      </c>
+      <c r="D12">
+        <v>579.1799999999999</v>
+      </c>
+      <c r="E12">
+        <v>2.43</v>
+      </c>
+      <c r="F12">
+        <v>-0.245182606478465</v>
+      </c>
+      <c r="G12">
+        <v>2.02</v>
+      </c>
+      <c r="H12">
+        <v>-0.5723080635497066</v>
+      </c>
+      <c r="I12">
+        <v>563.7499877929688</v>
+      </c>
+      <c r="J12">
+        <v>552.5349945068359</v>
+      </c>
+      <c r="K12">
+        <v>504.5963977050781</v>
+      </c>
+      <c r="L12">
+        <v>456.1688491821289</v>
+      </c>
+      <c r="M12">
         <v>1.02</v>
       </c>
-      <c r="P9">
-        <v>4</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>2.222222222222222</v>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" t="b">
-        <v>1</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>54.09</v>
-      </c>
-      <c r="Y9">
-        <v>92.16</v>
-      </c>
-      <c r="Z9">
-        <v>9.82</v>
-      </c>
-      <c r="AA9">
-        <v>12.82</v>
-      </c>
-      <c r="AB9">
-        <v>239.78</v>
-      </c>
-      <c r="AC9">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="AD9">
-        <v>10.92</v>
-      </c>
-      <c r="AE9">
-        <v>-14.06</v>
-      </c>
-      <c r="AF9">
-        <v>6.67</v>
-      </c>
-      <c r="AG9">
-        <v>89.47</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ9" t="s">
+      <c r="N12">
+        <v>1.12</v>
+      </c>
+      <c r="P12">
+        <v>6</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>275.5</v>
+      </c>
+      <c r="Y12">
+        <v>602.77</v>
+      </c>
+      <c r="Z12">
+        <v>18.38</v>
+      </c>
+      <c r="AA12">
+        <v>14.31</v>
+      </c>
+      <c r="AB12">
+        <v>9.6</v>
+      </c>
+      <c r="AC12">
+        <v>34.07</v>
+      </c>
+      <c r="AD12">
+        <v>7.55</v>
+      </c>
+      <c r="AE12">
+        <v>-19.56</v>
+      </c>
+      <c r="AF12">
+        <v>11.94</v>
+      </c>
+      <c r="AG12">
+        <v>48.89</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK12">
+        <v>15.97786966763727</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>97.57575757575758</v>
+      </c>
+      <c r="C13">
+        <v>481</v>
+      </c>
+      <c r="D13">
+        <v>295.8</v>
+      </c>
+      <c r="E13">
+        <v>1.91</v>
+      </c>
+      <c r="F13">
+        <v>-0.5339342475576336</v>
+      </c>
+      <c r="G13">
+        <v>2.03</v>
+      </c>
+      <c r="H13">
+        <v>-0.562199361340269</v>
+      </c>
+      <c r="I13">
+        <v>285.8079956054688</v>
+      </c>
+      <c r="J13">
+        <v>285.7139999389648</v>
+      </c>
+      <c r="K13">
+        <v>280.7178002929688</v>
+      </c>
+      <c r="L13">
+        <v>220.5402495574951</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1.02</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>124.53</v>
+      </c>
+      <c r="Y13">
+        <v>303.14</v>
+      </c>
+      <c r="Z13">
+        <v>20.84</v>
+      </c>
+      <c r="AA13">
+        <v>26.94</v>
+      </c>
+      <c r="AB13">
+        <v>6.3</v>
+      </c>
+      <c r="AC13">
+        <v>29.07</v>
+      </c>
+      <c r="AD13">
+        <v>4.79</v>
+      </c>
+      <c r="AE13">
+        <v>-10.48</v>
+      </c>
+      <c r="AF13">
+        <v>22.77</v>
+      </c>
+      <c r="AG13">
+        <v>17.44</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK13">
+        <v>6.238433683000013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>91.91919191919192</v>
+      </c>
+      <c r="C14">
+        <v>121</v>
+      </c>
+      <c r="D14">
+        <v>88.27</v>
+      </c>
+      <c r="E14">
+        <v>4.76</v>
+      </c>
+      <c r="F14">
+        <v>1.048646862203193</v>
+      </c>
+      <c r="G14">
+        <v>3.83</v>
+      </c>
+      <c r="H14">
+        <v>1.257367036358526</v>
+      </c>
+      <c r="I14">
+        <v>86.21599884033203</v>
+      </c>
+      <c r="J14">
+        <v>84.74049987792969</v>
+      </c>
+      <c r="K14">
+        <v>75.94139968872071</v>
+      </c>
+      <c r="L14">
+        <v>56.68014999389649</v>
+      </c>
+      <c r="M14">
+        <v>1.02</v>
+      </c>
+      <c r="N14">
+        <v>1.14</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>28.47</v>
+      </c>
+      <c r="Y14">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="Z14">
+        <v>7.07</v>
+      </c>
+      <c r="AA14">
+        <v>0.7</v>
+      </c>
+      <c r="AB14">
+        <v>457.63</v>
+      </c>
+      <c r="AC14">
+        <v>360.71</v>
+      </c>
+      <c r="AD14">
+        <v>2.87</v>
+      </c>
+      <c r="AE14">
+        <v>317.14</v>
+      </c>
+      <c r="AF14">
+        <v>-59.3</v>
+      </c>
+      <c r="AG14">
+        <v>253.57</v>
+      </c>
+      <c r="AH14" t="s">
         <v>61</v>
       </c>
-      <c r="AK9">
-        <v>67.75630911770669</v>
+      <c r="AI14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK14">
+        <v>86.81595048046601</v>
       </c>
     </row>
   </sheetData>
